--- a/samples/output/sample_mixed_types_field_report_strict.xlsx
+++ b/samples/output/sample_mixed_types_field_report_strict.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -575,11 +575,11 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9708</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>numeric_continuous</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -745,10 +745,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -767,13 +767,13 @@
         <v>0.925</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="5">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>numeric_continuous</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Count / Frequency Table — not recommended for visualization</t>
+          <t>Histogram, Box Plot, Violin Plot</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.93</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/samples/output/sample_mixed_types_field_report_strict.xlsx
+++ b/samples/output/sample_mixed_types_field_report_strict.xlsx
@@ -958,7 +958,7 @@
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Count / Frequency Table — not recommended for visualization ⚠ All unique — likely ID column</t>
+          <t>Count / Frequency Table — not recommended for visualization</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">

--- a/samples/output/sample_mixed_types_field_report_strict.xlsx
+++ b/samples/output/sample_mixed_types_field_report_strict.xlsx
@@ -563,7 +563,11 @@
       <c r="F3" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>numeric:200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -604,7 +608,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.775</v>
+        <v>0.85</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -617,7 +621,11 @@
       <c r="F5" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>str:200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -629,7 +637,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.6287</v>
+        <v>0.7036</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -642,7 +650,11 @@
       <c r="F6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>str:200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -792,13 +804,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.775</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="6">
@@ -817,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.9987</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6287</v>
+        <v>0.7036</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +967,11 @@
           <t>identifier</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>str:200</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Count / Frequency Table — not recommended for visualization</t>
@@ -965,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -979,7 +995,11 @@
           <t>categorical_low</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>str:200</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Bar Chart, Pie Chart (if ≤6 cats), Treemap</t>
@@ -989,7 +1009,7 @@
         <v>0.025</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="5">
@@ -1003,7 +1023,11 @@
           <t>numeric_continuous</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>numeric:200</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Histogram, Box Plot, Violin Plot ⚠ All unique — likely ID column</t>
